--- a/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx
+++ b/docs/03_詳細設計/04_クラス・内部IF設計/KF-DD-CLS-09_バッチ_クラス詳細設計書.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
     <row r="16">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：22 本のオンライン詳細設計書（ONL-001〜022）と 3 本のバッチ詳細設計書（BAT-001〜003）の規格 JSON をクラス単位に集約・再構成したもの。同一クラスのメソッドを複数 ONL / BAT が定義・追記している場合は統合し、重複を除いた。v2.0 で解消した食い違いと、なお残る食い違いは 4. に整理した。</t>
+          <t>本書の位置づけ：23 本のオンライン詳細設計書（ONL-001〜023）と 3 本のバッチ詳細設計書（BAT-001〜003）の規格 JSON、および実コードから起こした API-024〜026（ONL-024〜026。休憩・離席の打刻、部署一覧。専用の ONL 詳細設計書は未作成）を、クラス単位に集約・再構成したもの。同一クラスのメソッドを複数 ONL / BAT が定義・追記している場合は統合し、重複を除いた。解消した食い違いと、なお残る食い違い（実コード照合の結果を含む）は 4. に整理した。　【実装状況】本領域（バッチ 19 クラス）は設計のみで、現行の backend（com.example.kintaiflow）にはソースが存在しない（2026/10/05 の実コード照合）。</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>@Configuration（DevDataInitializer は CommandLineRunner 実装）</t>
+          <t>@Configuration（DevDataInitializer / BootstrapAdminInitializer は @Component の CommandLineRunner 実装）</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>@Configuration（DevDataInitializer は CommandLineRunner 実装）</t>
+          <t>@Configuration（DevDataInitializer / BootstrapAdminInitializer は @Component の CommandLineRunner 実装）</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -9344,7 +9344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9403,6 +9403,52 @@
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3" ht="49" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>実コードとの照合：backend（com.example.kintaiflow）に本領域のクラス（19 クラス）のソースは存在しないため、『設計のみ（未実装）』であることを明記。4. に整合性メモを追加。既存記述は変更なし</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="49" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>実コード再照合（2026/10/05 夜）：バッチ領域のソースは引き続き backend に存在しない（設計のみ）。記述の変更なし。他領域の追加に伴い、総覧との整合のみ再生成</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9962,7 +10008,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C32" s="8" t="n"/>
@@ -11133,7 +11179,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -12145,7 +12191,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -13961,7 +14007,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
@@ -14573,7 +14619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F62"/>
+  <dimension ref="A2:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14587,7 +14633,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>4.1 解消済み（v2.0）：更新済み規格で是正された食い違い（前版の報告分。規格 JSON を機械照合して確認）</t>
+          <t>4.1 解消済み：規格の更新・実装反映で是正された食い違い（前版までの報告分。規格 JSON と実コードを照合して確認）</t>
         </is>
       </c>
       <c r="B2" s="8" t="n"/>
@@ -14619,7 +14665,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>v2.0 の状態</t>
+          <t>現在の状態</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -14634,7 +14680,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>解消済み（v2.0）</t>
+          <t>解消済み</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -14658,350 +14704,354 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>4.2 未決事項・残る食い違い（v2.0 の検証で新たに見つかったもの／外部文書の課題）</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="5" ht="79" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>解消済み</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>LeaveBalanceRepository#findAlertBaseRows の定義統一（BAT-002 ↔ ONL-013）</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002 が別シグネチャ（AlertBaseRow 返却）の Repository 版を定義していた</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002 は ONL-013 の LeaveBalanceService#findAlertBaseRows(asOf) と Repository 版 findAlertBaseRows(leaveTypeId, minDays, asOf) を参照（再定義なし）。実コードにも ONL-013 版のみ存在する（AlertBaseRow クラスは設計のみ）</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>ONL-013, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>解消済み</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>NotificationService#existsMonthly の統一（BAT-002 ↔ ONL-019）</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019 と BAT-002 が別シグネチャ・別の重複判定キーを定義していた</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019 が 3 引数版と本文先頭キー付き 4 引数版 existsMonthly(userId, type, keyPrefix, yearMonth) を定義し、BAT-002 は 4 引数版を使用。実コードの NotificationService / NotificationRepository にも両方ある</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="49" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>解消済み</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>通知 type の定数化（BAT-001/002 ↔ ONL-005）</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>BAT が文字列リテラル LEAVE_GRANT / MANDATORY_LEAVE_ALERT を使い、notifications.type が保存されない前提だった</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>NotificationType.LEAVE_GRANTED / LEAVE_ALERT を使用。notifications.type・request_id は保存される（V1__init_schema.sql に列と FK がある）</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>ONL-005, BAT-001, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>解消済み</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>失効日の規則（BAT-001）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001 の接点表が『失効日当日は無効』と記載</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>全 ONL / BAT で expires_on &gt;= 基準日（失効日当日は有効）</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ONL-013, BAT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>4.2 未決事項・残る食い違い（実コード照合で確認した設計↔実装の差異／規格間の差異／外部文書の課題）</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>詳細（記述の食い違い）</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>統一方針・対応</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>関連 ONL / BAT</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="12" ht="79" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>設計↔実装</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>バッチ（BAT-001〜003）のクラス 19 個が実コードに存在しない</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>BackupBatch / LeaveGrantBatch / MandatoryLeaveAlertBatch ほか領域 09 の 19 クラス（BatchResult・BatchStatus・SchedulingConfig を含む）は設計のみで、backend にソースが無い。KintaiflowApplication にも @EnableScheduling 等のバッチ起動の記述は無い。</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-CLS-09 は『設計（未実装）』として維持する。実装時に実コードと再照合する（未決）</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001, BAT-002, BAT-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="49" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>例外</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>LeaveBalanceRepository#findAlertBaseRows の例外記述が ONL 間で異なる（一方は「なし」）</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ONL-013: なし；BAT-002: DataAccessException</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>具体的に記述している側を採用（実行時例外 PessimisticLockingFailureException 等は共通で E-012）</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>ONL-013, BAT-002</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="139" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>BAT↔ONL</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>LeaveBalanceRepository#findAlertBaseRows が ONL-013 と BAT-002 で別定義（引数・戻り値・抽出条件が異なる）</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ONL-013: findAlertBaseRows(Long leaveTypeId, BigDecimal minDays, LocalDate asOf) : List&lt;LeaveBalance&gt;、条件 expires_on &gt;= asOf。BAT-002: findAlertBaseRows(Long typeId, LocalDate floor, LocalDate today) : List&lt;AlertBaseRow&gt;（User JOIN の射影）、条件 granted_on &gt;= floor で expires_on 条件なし。ONL-013 / ONL-019 は『BAT-002 は LeaveBalanceService#findAlertBaseRows を使う』と記載するが、BAT-002 は Repository を直接呼び Service 版を使わない。</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002 の Repository 版（AlertBaseRow、N+1 回避）を採用し、ONL-013 の Service#findAlertBaseRows と Repository 版は廃止、または名称を分けて併存させる。どちらかに統一する規格改訂が必要（実装時は同名オーバーロードにしない）</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>ONL-013, ONL-019, BAT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>BAT↔ONL</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001 が参照する失効日の規則が『当日は無効』と記載されている</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001 の接点表に『失効日の規則（当日は無効）』とあるが、ONL-005 / 010 / 013 / 017 は確定設計変更 D4 により expires_on &gt;= 基準日（当日は有効）。付与行を作る BAT-001 の処理自体（granted_on + 2年）には影響しない。</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001 の記述を『失効日当日は有効（expires_on &gt;= 基準日）』に改訂（実装影響なし）</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ONL-013, BAT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="124" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>NotificationRepository#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan の例外記述が ONL 間で異なる（一方は「なし」）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019: なし；BAT-002: DataAccessException</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>具体的に記述している側を採用（実行時例外 PessimisticLockingFailureException 等は共通で E-012）</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019, BAT-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="124" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>notifications.is_read のフィールド名・型が ONL / BAT 間で異なる</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ONL-005: read / boolean / NULL 不可；ONL-008: read / boolean / NULL 不可；ONL-010: read / boolean / NULL 不可；ONL-011: read / boolean / NULL 不可；ONL-012: read / boolean / NULL 不可；ONL-017: read / boolean / NULL 不可；ONL-019: read / boolean / NULL 不可；ONL-022: read / boolean / NULL 不可；BAT-001: isRead / Boolean / NULL 不可；BAT-002: read / boolean / NULL 不可</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>定義元 ONL の表記に統一（ONL-019 の Notification：フィールド read、boolean、getter isRead()）。BAT-001 / BAT-002 のマッピング表の修正が必要</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>ONL-005, ONL-008, ONL-010, ONL-011, ONL-012, ONL-017, ONL-019, ONL-022, BAT-001, BAT-002</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="139" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>BAT↔ONL</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>NotificationService#existsMonthly が ONL-019 と BAT-002 で別シグネチャ（重複判定のキーも異なる）</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019: existsMonthly(Long userId, String type, YearMonth yearMonth)＝type と月で判定（NotificationRepository#existsByUserIdAndTypeAndCreatedAtGreaterThanEqualAndCreatedAtLessThan）。BAT-002: existsMonthly(Long userId, String likePattern, LocalDateTime from, LocalDateTime to)＋NotificationRepository#existsMonthlyByPattern＝本文の前方一致（selfPrefix / adminPrefix）で判定。BAT-002 は『ONL-019 は一覧取得・既読化のみ定義』と記載しており ONL-019 の現状と食い違う。</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>type が保存される（ONL-005 D-16）ため、本人宛て／管理者宛てを type で区別できるなら ONL-019 版に統一。区別できないなら BAT-002 版を別名（例 existsMonthlyByMessagePrefix）にして併存。規格改訂が必要</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019, BAT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="94" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>BAT↔ONL</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>BAT の通知 type 値が NotificationType 定数と不一致で、保存有無の記述も古い</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001 は notify(userId, "LEAVE_GRANT", …)、BAT-002 は "MANDATORY_LEAVE_ALERT" を渡す。ONL-005 の NotificationType は LEAVE_GRANTED / LEAVE_ALERT（7 値）。また BAT-001 D-13・BAT-002 は『notifications に type / request_id 列が無く保存されない』と記載するが、ONL-005 D-16 は保存に変更済み。</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>NotificationType.LEAVE_GRANTED / LEAVE_ALERT の定数を使用（文字列リテラルを使わない）。BAT-001 / BAT-002 の記述（D-13 ほか）を『保存される』に改訂</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>ONL-005, BAT-001, BAT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>4.3 ONL / BAT 内の決定事項（参考：各 ONL が既存設計の不足・矛盾に対して下した判断）</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>ONL</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>決定内容</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>理由・影響</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="49" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="49" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>D-1</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>応当日の算出規則</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>初回付与日 first = hire_date.plusMonths(6)、n 回目（n=0,1,2…）の付与日 = first.plusYears(n)。毎回 first を起点に加算し、前回付与日からの加算は行わない。</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>ONL-013 の calcNextGrantDate と同一規則（表示用の次回付与予定日とバッチの実付与日が一致する）。前回日起点だと 2/29 の丸めが累積してずれるため。</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="79" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>D-2</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>月末入社の扱い</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Java/PostgreSQL ともに「応当日が存在しない月は月末へ丸める」。例: 入社 2026-08-31 → 初回 2027-02-28、2回目 2028-02-28（2028-02-29 ではない）。民法143条の厳密な読み（6か月満了日の翌日 = 2027-03-01）より最大 1 日早い。</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>付与が早い側に倒れるため労基法違反にならず、実装と SQL を単純に保てる。1日の差は許容（KF-DD-004 の付与日数表は日単位の厳密性を求めていない）。</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19" ht="79" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>D-3</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>うるう年</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>first が 2/29 になるのは「うるう年の 2/29 に応当する入社日（前年 8/29〜8/31 入社 → 当年 2/28 or 2/29）」。平年は 2/28、うるう年は 2/29 に付与（first.plusYears(n) の結果）。入社日自体が 2/29 の場合は 6か月後 8/29 で問題なし。</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>LocalDate#plusYears の仕様に従う（PostgreSQL の date + n * interval '1 year' と同じ結果）。付与日は常に first から直接計算するので、2/28 に丸められた年の翌年以降も元の日付に戻る（2028-02-29）。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -15009,139 +15059,139 @@
     <row r="20" ht="79" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>月末入社の扱い</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Java/PostgreSQL ともに「応当日が存在しない月は月末へ丸める」。例: 入社 2026-08-31 → 初回 2027-02-28、2回目 2028-02-28（2028-02-29 ではない）。民法143条の厳密な読み（6か月満了日の翌日 = 2027-03-01）より最大 1 日早い。</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>付与が早い側に倒れるため労基法違反にならず、実装と SQL を単純に保てる。1日の差は許容（KF-DD-004 の付与日数表は日単位の厳密性を求めていない）。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="79" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>うるう年</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>first が 2/29 になるのは「うるう年の 2/29 に応当する入社日（前年 8/29〜8/31 入社 → 当年 2/28 or 2/29）」。平年は 2/28、うるう年は 2/29 に付与（first.plusYears(n) の結果）。入社日自体が 2/29 の場合は 6か月後 8/29 で問題なし。</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>LocalDate#plusYears の仕様に従う（PostgreSQL の date + n * interval '1 year' と同じ結果）。付与日は常に first から直接計算するので、2/28 に丸められた年の翌年以降も元の日付に戻る（2028-02-29）。</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="79" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>D-4</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>付与日数の決定方法</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>勤続月数を ChronoUnit.MONTHS.between で求めず、付与回数 n から statutoryDays(6 + 12 × n) を呼ぶ（n=0→10日, 1→11, 2→12, 3→14, 4→16, 5→18, 6以上→20）。</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>月末入社（例: 入社 8/31・付与日 2/28）では MONTHS.between が 5 になり statutoryDays が 0 を返してしまう。ONL-017 の listGrants も付与回数ベース（regularGrantCount → statutoryDays(6 + 12 × 付与回数)）に変更済みで、本書と同じ考え方に揃っている。</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>D-5</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>付与日と取りこぼし救済</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>granted_on は実行日ではなく応当日。毎回 [本日−catch-up-days, 本日] の各日を判定する（既定 7 日、kintaiflow.batch.leave-grant.catch-up-days）。通常運用では応当日＝本日。</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>アプリ停止・障害で 02:00 を逃しても、7日以内の復旧なら次回実行で付与される。冪等のため重複しない。7日を超えた漏れは 7.2 の確認 SQL で検出し、run-once の target-date 指定または SCR-305 で付与する。</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="154" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="154" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>D-6</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>冪等キーと二重付与の防止</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>(user_id, leave_type_id, granted_on)。二段構え: (1) users 行ロックの内側で事前 NOT EXISTS チェック（existsByUserIdAndLeaveTypeIdAndGrantedOn）。(2) DB の UNIQUE 制約 uq_leave_balances_1 (user_id, leave_type_id, granted_on)（schema.sql に追加済み）が最終防衛。(2) に当たった DataIntegrityViolationException は LeaveGrantService#execute（トランザクションの外側）で握り、existsBy… で再確認して存在すれば『既付与』として SKIP（WARN BAT001-W03）、存在しなければ別の整合性違反として失敗（BAT001-E03）に数える。</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>ONL-017 の決定（D-4）と同じ判定単位で、手動付与（E-013）とも整合する。grantOne の内側で握らないのは、PostgreSQL ではエラー後のトランザクションが中止状態になり以降の SQL（通知 INSERT）を実行できないため。再確認により FK 違反などを誤って SKIP しない。</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="49" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>D-7</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>トランザクション境界</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>ユーザー×応当日 1 件 = 1 トランザクション（REQUIRES_NEW）。ループ側（LeaveGrantService）は非トランザクション。</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>ループ全体を 1 トランザクションにすると 1 件の失敗（PostgreSQL ではエラー後のトランザクションは中止状態）で全件ロールバックになるため。</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>D-8</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>排他制御</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>ユーザー行を SELECT … FOR UPDATE（UserRepository#findByIdForUpdate）してから再判定・存在確認・INSERT する。ロック順は users → leave_balances（ONL-017 と同じ）。</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>SCR-305 の手動付与（ONL-017）と同時刻に重なっても直列化される。ロック待ちは lock.timeout=5000ms、超過は当該件の失敗（BAT001-E03）。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -15149,279 +15199,279 @@
     <row r="25" ht="49" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>トランザクション境界</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー×応当日 1 件 = 1 トランザクション（REQUIRES_NEW）。ループ側（LeaveGrantService）は非トランザクション。</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ループ全体を 1 トランザクションにすると 1 件の失敗（PostgreSQL ではエラー後のトランザクションは中止状態）で全件ロールバックになるため。</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>排他制御</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー行を SELECT … FOR UPDATE（UserRepository#findByIdForUpdate）してから再判定・存在確認・INSERT する。ロック順は users → leave_balances（ONL-017 と同じ）。</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>SCR-305 の手動付与（ONL-017）と同時刻に重なっても直列化される。ロック待ちは lock.timeout=5000ms、超過は当該件の失敗（BAT001-E03）。</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="49" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>D-9</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>対象外とした法的要件</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>出勤率8割以上の判定、週所定労働日数が少ない者への比例付与、パート・時間単位年休は対象外（KF-DD-004 の MVP 簡略化に従う）。例外は管理者が SCR-305 で調整。</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>要件定義の範囲外。付与日数表は週所定5日以上・フルタイム前提。</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="79" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="79" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>D-10</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>手動実行</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>手動実行用の管理 API は作らない。障害時は BatchRunOnceRunner（--kintaiflow.batch.run-once=BAT-001 [--kintaiflow.batch.target-date=yyyy-MM-dd]）で 1 回だけ実行し、終了コード（0/1/2）を返して JVM を終了する。テストでは LeaveGrantService#execute(LocalDate) を直接呼ぶ。</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>API を公開すると認可・監査の設計が増えるため。コマンドラインなら OS の権限で保護される。</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="94" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="94" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>D-11</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>複数インスタンスへの将来対応</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>現状は単一インスタンス前提。複数台にする場合は ShedLock（net.javacrumbs.shedlock）を導入し、shedlock テーブルと @SchedulerLock(name="BAT-001", lockAtMostFor="PT30M", lockAtLeastFor="PT1M") を付与する。本書の冪等設計はそのままで二重付与は起きないため、導入しても処理ロジックは変更不要。</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>現段階で ShedLock を入れると依存とテーブルが増える。冪等＋行ロックで安全性は確保済み。</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="49" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="49" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>D-12</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>要件定義書の参照</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>KF-RD-001（PDF）は docs/01_要件定義 に未配置のため参照できなかった。法的根拠は労働基準法の条文（第39条・第115条）から直接記載した。</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>要件定義書の配置後に付与日数・失効規則との齟齬がないか照合する。</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29" ht="109" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="109" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>D-13</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>通知の type / requestId</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>NotificationService#notify(Long userId, String type, String message, Long requestId) を type=NotificationType.LEAVE_GRANTED（"LEAVE_GRANTED"）、requestId=null で呼ぶ（ONL-017 と同じ）。type は notifications.type（VARCHAR(30)）に保存され、request_id は NULL。本文は buildGrantMessage を再利用し「理由：勤続6か月の法定付与」等を付ける。</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>画面（SCR-101）に出る文言・種別を手動付与と揃える。LEAVE_GRANTED は申請に紐づかないため requestId は null（notify の入力検証でも REQUEST_BOUND 以外は null 可）。</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="79" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="79" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>D-14</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>対象ユーザー</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>status='ACTIVE' のみ。休職・退職で INACTIVE の間に迎えた応当日は付与しない（復帰後の遡及付与は管理者が SCR-305 で行う）。hire_date を後から修正した場合は、修正後の応当日で判定する（抽出後に修正されても grantOne が行ロック内で再判定）。</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>INACTIVE は退職・休職（KF-BD-005）。</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="49" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>D-15</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>スケジューラ設定</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>spring.task.scheduling.pool.size=3、シャットダウン時は実行中のバッチ完了を最大 60 秒待つ（await-termination）。ログのスレッド名は kf-batch-N。</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>既定のスレッド数 1 では 03:00 の BAT-002 が BAT-001 の遅延に巻き込まれる。</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="109" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="109" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>D-16</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>updated_at とタイムゾーン</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>leave_balances.updated_at は DB トリガ trg_leave_balances_updated_at（BEFORE UPDATE / set_updated_at）が更新時に自動更新する（INSERT 時は DEFAULT CURRENT_TIMESTAMP）。バッチ・Entity は created_at / updated_at を設定しない。DB セッションの JST は hikari connection-init-sql `SET TIME ZONE 'Asia/Tokyo'` で設定済み（ONL-002 の 7.3）。</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>旧版の『DB の timezone 設定が必須』を『設定済み』に変更。ALTER DATABASE による設定は不要（接続のたびに設定されるため）。</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33" ht="64" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>D-17</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>失効日の扱い</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>expires_on = granted_on.plusYears(2)（LeaveBalanceService#grant 内で算出）。失効日当日は有効で、有効判定は expires_on &gt;= 基準日（ONL-013）。BAT-001 自身は失効判定を行わない（付与のみ）。</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>ONL-013/017 で統一した規則（expires_on は最終有効日）に合わせた。</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34" ht="94" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>対象の基準行（直近の付与）</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>LeaveBalanceService#findAlertBaseRows(本日)（ONL-013）が返す年休付与行（ACTIVE・granted_days ≧ 10・granted_on ≦ 本日・expires_on ≧ 本日・本日 &lt; granted_on + 1年）から、ユーザーごとに granted_on が最新の1行（並び順 user_id, granted_on DESC, id DESC の先頭）を基準行とする。</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>ONL-013 の calcMandatory5 と同じ選び方・同じ抽出条件を共有する（BAT-002 側で SQL を再実装しない）。付与日数が10日未満の期（比例付与など）や、義務期間が終了した付与は対象外。繰越分は付与日数に含めない（当期に付与された日数のみで10日判定）。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -15429,55 +15479,55 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-17</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>失効日の扱い</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>expires_on = granted_on.plusYears(2)（LeaveBalanceService#grant 内で算出）。失効日当日は有効で、有効判定は expires_on &gt;= 基準日（ONL-013）。BAT-001 自身は失効判定を行わない（付与のみ）。</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>ONL-013/017 で統一した規則（expires_on は最終有効日）に合わせた。</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="94" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>9か月経過の判定</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>granted_on.plusMonths(9) ≦ 本日（当日を含む）。月初 1 日にしか実行しないため、実際の初回通知は『付与日+9か月 以降で最初に来る 1 日』。例: 付与 2025-10-01 → 2026-07-01 が初回。付与 2025-10-15 → 2026-08-01。</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>KF-DD-004『付与日から9か月以上経過』を文字どおり実装。plusMonths の月末丸めは Java 標準に従う。</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36" ht="79" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>D-3</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>取得日数の集計</t>
+          <t>対象の基準行（直近の付与）</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>承認済み（requests.status='APPROVED'）の休暇申請（request_type='LEAVE'）で leave_type_id=年休のものの days 合計（半日 0.5 を含む）。期間は start_date が [付与日, 付与日+1年−1日]。既存の RequestRepository#sumApprovedLeaveDays（ONL-013）をそのまま再利用する。</t>
+          <t>LeaveBalanceService#findAlertBaseRows(本日)（ONL-013）が返す年休付与行（ACTIVE・granted_days ≧ 10・granted_on ≦ 本日・expires_on ≧ 本日・本日 &lt; granted_on + 1年）から、ユーザーごとに granted_on が最新の1行（並び順 user_id, granted_on DESC, id DESC の先頭）を基準行とする。</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>ONL-013 の『開始日で期間判定、期間をまたぐ申請は開始日側に全日数を計上』と揃える（MVP の簡略化）。leave_balances.used_days は FIFO 消化で期をまたぐため使わない。</t>
+          <t>ONL-013 の calcMandatory5 と同じ選び方・同じ抽出条件を共有する（BAT-002 側で SQL を再実装しない）。付与日数が10日未満の期（比例付与など）や、義務期間が終了した付与は対象外。繰越分は付与日数に含めない（当期に付与された日数のみで10日判定）。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -15485,83 +15535,83 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>D-2</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>9か月経過の判定</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>granted_on.plusMonths(9) ≦ 本日（当日を含む）。月初 1 日にしか実行しないため、実際の初回通知は『付与日+9か月 以降で最初に来る 1 日』。例: 付与 2025-10-01 → 2026-07-01 が初回。付与 2025-10-15 → 2026-08-01。</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>KF-DD-004『付与日から9か月以上経過』を文字どおり実装。plusMonths の月末丸めは Java 標準に従う。</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="79" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>取得日数の集計</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>承認済み（requests.status='APPROVED'）の休暇申請（request_type='LEAVE'）で leave_type_id=年休のものの days 合計（半日 0.5 を含む）。期間は start_date が [付与日, 付与日+1年−1日]。既存の RequestRepository#sumApprovedLeaveDays（ONL-013）をそのまま再利用する。</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>ONL-013 の『開始日で期間判定、期間をまたぐ申請は開始日側に全日数を計上』と揃える（MVP の簡略化）。leave_balances.used_days は FIFO 消化で期をまたぐため使わない。</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>D-4</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>将来日の承認済み申請</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>対象期間内であれば、利用日が未来の承認済み申請も取得日数に含める（計画的な取得とみなす）。</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>『承認済みの休暇申請の日数』という指示どおり。取得が確定した日だけで厳密に数える場合は start_date ≦ 本日 を条件に追加する（変更が必要になれば sumApprovedLeaveDays に上限日を渡す）。</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>通知先</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>(1) 本人、(2) users.role='ADMIN' かつ status='ACTIVE' の全員。対象者本人が ADMIN の場合は管理者向けを省き本人向けの 1 件だけにする。上長（MANAGER）へは通知しない（KF-DD-004 の仕様どおり）。</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>管理者が 0 名なら WARN を出し、本人分のみ登録する。</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39" ht="139" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>D-6</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>同月重複通知の防止（type 列＋本文先頭の対象者キー）</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>NotificationType.LEAVE_ALERT で notify し、次の4条件で判定する。(a) type='LEAVE_ALERT'、(b) 宛先 user_id、(c) message が先頭キー `[対象者ID:{id} 付与日:{yyyy-MM-dd}]` で始まる（対象者・付与日の特定。本人宛て・管理者宛てとも同じ書式で先頭に付ける）、(d) created_at が当月1日 00:00 以上 翌月1日 00:00 未満（JST）。判定は NotificationService#existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth)（本書で ONL-019 の 3 引数版に追加する overload）。</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>ONL-019 の existsMonthly(userId, type, yearMonth) は対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版だと 2 人目以降が『送信済み』と誤判定されて通知されない。notifications に対象者を特定する列が無いため、本文先頭のキーで補う（] で閉じるので ID:1 と ID:12 を区別できる）。DB 制約ではなく、同時実行では重複しうる（単一インスタンスなら実害なし）。代替案の dedup_key 列追加は 7.4 に残す。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -15569,251 +15619,251 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>通知先</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(1) 本人、(2) users.role='ADMIN' かつ status='ACTIVE' の全員。対象者本人が ADMIN の場合は管理者向けを省き本人向けの 1 件だけにする。上長（MANAGER）へは通知しない（KF-DD-004 の仕様どおり）。</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>管理者が 0 名なら WARN を出し、本人分のみ登録する。</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="139" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>同月重複通知の防止（type 列＋本文先頭の対象者キー）</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>NotificationType.LEAVE_ALERT で notify し、次の4条件で判定する。(a) type='LEAVE_ALERT'、(b) 宛先 user_id、(c) message が先頭キー `[対象者ID:{id} 付与日:{yyyy-MM-dd}]` で始まる（対象者・付与日の特定。本人宛て・管理者宛てとも同じ書式で先頭に付ける）、(d) created_at が当月1日 00:00 以上 翌月1日 00:00 未満（JST）。判定は NotificationService#existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth)（本書で ONL-019 の 3 引数版に追加する overload）。</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>ONL-019 の existsMonthly(userId, type, yearMonth) は対象者・付与日を区別できない。管理者は同じ月に複数の対象者分を受け取るため、3 引数版だと 2 人目以降が『送信済み』と誤判定されて通知されない。notifications に対象者を特定する列が無いため、本文先頭のキーで補う（] で閉じるので ID:1 と ID:12 を区別できる）。DB 制約ではなく、同時実行では重複しうる（単一インスタンスなら実害なし）。代替案の dedup_key 列追加は 7.4 に残す。</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>D-7</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>『同月』の定義</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>判定する月は実行時点（Clock）の暦月（JST）。run-once の target-date は期間判定にのみ使い、同月判定には使わない。</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>created_at は実際の登録時刻（DB の現在時刻）になるため、実行時点の月と比較しないと整合しない。DB セッション TZ が JST であることが前提（hikari connection-init-sql で設定済み）。</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41" ht="49" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="49" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>D-8</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>通知文中の期限は granted_on.plusYears(1).minusDays(1)（付与日から1年以内の最終日）。月初しか実行しないため最終通知は期限の最大約1か月前になる。</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>毎月1回の運用でも、9〜12か月目の間に 1〜4 回の通知がある。通知頻度を上げる場合は cron のみ変更すればよい（同月重複は防止される）。</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>D-9</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>トランザクション</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>未達の対象者 1 人 = 1 Tx（REQUIRES_NEW）。集計（読み取り）は Tx 外。</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>BAT-001 D-7 と同じ理由。</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>D-10</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>手動実行</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>管理 API は作らない。BatchRunOnceRunner（--kintaiflow.batch.run-once=BAT-002 [--kintaiflow.batch.target-date=yyyy-MM-dd]）。テストでは MandatoryLeaveAlertService#execute(LocalDate) を直接呼ぶ。</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>BAT-001 D-10 と同じ。</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>D-11</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>複数インスタンス</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>現状は単一インスタンス前提。将来は ShedLock（@SchedulerLock(name="BAT-002", lockAtMostFor="PT30M")）を導入。導入しても本書のロジックは変更不要。重複通知の厳密な防止が必要なら 7.4 の dedup_key 案を併用する。</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>BAT-001 D-11 と同じ。</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>D-12</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>出勤率・計画的付与・時間単位</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>出勤率8割未満で付与されない場合は付与行が無いため対象外。年休の計画的付与（労使協定）、時間単位年休は対象外。</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>MVP の範囲外。</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>D-13</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>要件定義書の参照</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>KF-RD-001（PDF）は docs/01_要件定義 に未配置のため、法的根拠は労働基準法の条文から記載した。</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>配置後に照合する。</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
-    </row>
-    <row r="47" ht="79" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>D-14</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>notify の呼び出し</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>NotificationService#notify(Long userId, String type, String message, Long requestId) を type=NotificationType.LEAVE_ALERT、requestId=null で呼ぶ（ONL-005/019 の呼出し契約どおり）。本人宛て・管理者宛てとも同じ type。type / request_id は notifications に保存される。</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>LEAVE_ALERT は申請に紐づかないため requestId は null（REQUEST_BOUND 以外は null 可）。type で SCR-101 の表示分けや重複判定ができる。</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48" ht="49" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>D-15</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>失効日当日の扱い</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>対象行の有効判定は expires_on ≧ 本日（失効日当日は有効）。findAlertBaseRows 内で行い、BAT-002 では再判定しない。</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>ONL-013 で統一した規則。年休は付与から2年有効のため、実際の絞り込みは義務期間（1年）の側で効く。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -15821,7 +15871,7 @@
     <row r="49" ht="79" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -15831,45 +15881,45 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>updated_at・タイムゾーン</t>
+          <t>notify の呼び出し</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>notifications は INSERT のみ。updated_at は DEFAULT／UPDATE 時のみ DB トリガ trg_notifications_updated_at で自動更新され、バッチは設定しない。DB セッションの JST は hikari connection-init-sql で設定済み（ONL-002 の 7.3）。</t>
+          <t>NotificationService#notify(Long userId, String type, String message, Long requestId) を type=NotificationType.LEAVE_ALERT、requestId=null で呼ぶ（ONL-005/019 の呼出し契約どおり）。本人宛て・管理者宛てとも同じ type。type / request_id は notifications に保存される。</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>旧版の『DB の timezone 設定が必須』を『設定済み』に変更。</t>
+          <t>LEAVE_ALERT は申請に紐づかないため requestId は null（REQUEST_BOUND 以外は null 可）。type で SCR-101 の表示分けや重複判定ができる。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
     </row>
-    <row r="50" ht="139" customHeight="1">
+    <row r="50" ht="49" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>BAT-003</t>
+          <t>BAT-002</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>ダンプ形式: プレーン SQL（--format=plain）</t>
+          <t>失効日当日の扱い</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>拡張子 .sql のプレーン SQL とする。復元は psql。</t>
+          <t>対象行の有効判定は expires_on ≧ 本日（失効日当日は有効）。findAlertBaseRows 内で行い、BAT-002 では再判定しない。</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>理由: (1) KF-DD-004 のファイル名 backup/kintai_yyyyMMdd.sql と一致、(2) 中身をテキストで確認・grep・差分比較でき学習用途に向く、(3) 復元に psql だけでよく手順が単純、(4) データが小さく圧縮や並列復元の利点が小さい、(5) 1 テーブルだけを戻す場合もテキスト編集で対応できる。欠点: 圧縮されない、pg_restore による選択復元・並列復元ができない。1GB を超えるか部分復元が頻繁になった場合はカスタム形式（-Fc、拡張子 .dump）へ変更し、リストアを pg_restore に切り替える（8.7 に手順を併記）。</t>
+          <t>ONL-013 で統一した規則。年休は付与から2年有効のため、実際の絞り込みは義務期間（1年）の側で効く。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -15877,83 +15927,83 @@
     <row r="51" ht="79" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>updated_at・タイムゾーン</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>notifications は INSERT のみ。updated_at は DEFAULT／UPDATE 時のみ DB トリガ trg_notifications_updated_at で自動更新され、バッチは設定しない。DB セッションの JST は hikari connection-init-sql で設定済み（ONL-002 の 7.3）。</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>旧版の『DB の timezone 設定が必須』を『設定済み』に変更。</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="139" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>ダンプ形式: プレーン SQL（--format=plain）</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>拡張子 .sql のプレーン SQL とする。復元は psql。</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>理由: (1) KF-DD-004 のファイル名 backup/kintai_yyyyMMdd.sql と一致、(2) 中身をテキストで確認・grep・差分比較でき学習用途に向く、(3) 復元に psql だけでよく手順が単純、(4) データが小さく圧縮や並列復元の利点が小さい、(5) 1 テーブルだけを戻す場合もテキスト編集で対応できる。欠点: 圧縮されない、pg_restore による選択復元・並列復元ができない。1GB を超えるか部分復元が頻繁になった場合はカスタム形式（-Fc、拡張子 .dump）へ変更し、リストアを pg_restore に切り替える（8.7 に手順を併記）。</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="79" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>D-2</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>接続情報とパスワード</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>ホスト・ポート・DB 名・ユーザーは設定（環境変数から展開）。パスワードは環境変数 DB_PASSWORD を BackupProperties に読み込み、pg_dump プロセスの環境変数 PGPASSWORD にだけ設定する。コマンドライン引数・ログ・例外メッセージ・toString には出さない。</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>引数に書くと ps で他ユーザーに見える。.pgpass 方式（~/.pgpass、0600）も運用上は可。どちらも使える構成にするため PGPASSWORD は『設定されていれば渡す』とする。</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52" ht="79" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>D-3</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>BAT-003</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>pg_dump のオプション</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>--format=plain --no-owner --no-privileges --clean --if-exists --encoding=UTF8 --no-password --file=&lt;一時ファイル&gt;。</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>--no-owner / --no-privileges: 別ロールの環境へ復元しやすい。--clean --if-exists: 既存オブジェクトを DROP IF EXISTS してから作成するので、既存 DB 上でも空の DB 上でもエラーなく復元できる。--no-password: パスワード入力待ちで固まるのを防ぐ。</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>D-4</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>BAT-003</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>一時ファイル経由</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>kintai_yyyyMMdd.sql.tmp へ出力 → 検証 → ATOMIC_MOVE で最終名へ。失敗時は .tmp を削除。</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>途中で失敗・停止した壊れたファイルが世代として数えられるのを防ぐ。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -15961,7 +16011,7 @@
     <row r="54" ht="79" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -15971,25 +16021,25 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>世代管理</t>
+          <t>pg_dump のオプション</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>対象は『kintai_ + 8桁 + .sql』に完全一致するファイルだけ。ファイル名の日付降順に並べ、新しい 7 件を残して古いものを削除する（更新時刻ではなくファイル名の日付で判定）。新ダンプの検証・移動が成功した後にのみ実行する。名前が一致しないファイルは決して消さない。</t>
+          <t>--format=plain --no-owner --no-privileges --clean --if-exists --encoding=UTF8 --no-password --file=&lt;一時ファイル&gt;。</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ファイルを手動コピーしても世代判定がずれない。失敗時に世代が減らない。</t>
+          <t>--no-owner / --no-privileges: 別ロールの環境へ復元しやすい。--clean --if-exists: 既存オブジェクトを DROP IF EXISTS してから作成するので、既存 DB 上でも空の DB 上でもエラーなく復元できる。--no-password: パスワード入力待ちで固まるのを防ぐ。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
     </row>
-    <row r="55" ht="64" customHeight="1">
+    <row r="55" ht="34" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -15999,17 +16049,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>成功の検証</t>
+          <t>一時ファイル経由</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>(1) 最終ファイルが存在し通常ファイルである、(2) サイズが min-size-bytes（既定 1024）以上、(3) 末尾 1KB に pg_dump のプレーン出力の完了マーカー『-- PostgreSQL database dump complete』がある。いずれか不成立は失敗。</t>
+          <t>kintai_yyyyMMdd.sql.tmp へ出力 → 検証 → ATOMIC_MOVE で最終名へ。失敗時は .tmp を削除。</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>終了コード 0 でもディスクフル等での途中切れを検出するため。</t>
+          <t>途中で失敗・停止した壊れたファイルが世代として数えられるのを防ぐ。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
@@ -16017,111 +16067,111 @@
     <row r="56" ht="79" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>世代管理</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>対象は『kintai_ + 8桁 + .sql』に完全一致するファイルだけ。ファイル名の日付降順に並べ、新しい 7 件を残して古いものを削除する（更新時刻ではなくファイル名の日付で判定）。新ダンプの検証・移動が成功した後にのみ実行する。名前が一致しないファイルは決して消さない。</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>ファイルを手動コピーしても世代判定がずれない。失敗時に世代が減らない。</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57" ht="64" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>成功の検証</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>(1) 最終ファイルが存在し通常ファイルである、(2) サイズが min-size-bytes（既定 1024）以上、(3) 末尾 1KB に pg_dump のプレーン出力の完了マーカー『-- PostgreSQL database dump complete』がある。いずれか不成立は失敗。</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>終了コード 0 でもディスクフル等での途中切れを検出するため。</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="79" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>D-7</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>失敗時の扱い</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>pg_dump が非ゼロ終了／タイムアウト／検証失敗／I/O 失敗 → ERROR ログ（BAT003-E01〜E04）、BatchResult(failed=1)＝status=FAILED（run-once の終了コード 2）。自動リトライはしない。古い世代は削除しない。</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>スケジュール起動の Web アプリは JVM を終了させないため、『非ゼロ終了コード』は pg_dump の終了コードと run-once 実行の終了コードの 2 つを指す。監視は ERROR ログと END 行（8.5）。リトライはディスク満杯等の原因を隠すだけなので行わず、運用で手動再実行する。</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>D-8</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>ファイル権限</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>保存先ディレクトリ 700（rwx------）、ダンプ 600（rw-------）にする（POSIX 環境のみ。Windows は無視）。</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>パスワードハッシュ・氏名等の個人情報を含むため。</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58" ht="64" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>D-9</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>BAT-003</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>保存先</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>既定は実行ディレクトリ相対の backup/。本番は絶対パス（例 /var/backups/kintaiflow）を設定する。DB と同じディスクに置かないことを推奨し、別媒体・別ホストへのコピー（オフサイト）は本バッチの範囲外（運用課題）。</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>DB サーバーのディスク障害時にバックアップも失われるのを避けるため。</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59" ht="64" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>BAT-003</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>pg_dump の入手</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>アプリ稼働ホストに postgresql-client-18 をインストールし、pg-dump-path（既定 pg_dump = PATH 探索）を設定。DB サーバーが別ホストでもネットワーク越しに取得できる。pg_dump のメジャーバージョンはサーバー以上にする。</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>古い pg_dump は新しいサーバーに接続できない。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -16129,92 +16179,148 @@
     <row r="60" ht="64" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>D-9</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>保存先</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>既定は実行ディレクトリ相対の backup/。本番は絶対パス（例 /var/backups/kintaiflow）を設定する。DB と同じディスクに置かないことを推奨し、別媒体・別ホストへのコピー（オフサイト）は本バッチの範囲外（運用課題）。</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>DB サーバーのディスク障害時にバックアップも失われるのを避けるため。</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>pg_dump の入手</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>アプリ稼働ホストに postgresql-client-18 をインストールし、pg-dump-path（既定 pg_dump = PATH 探索）を設定。DB サーバーが別ホストでもネットワーク越しに取得できる。pg_dump のメジャーバージョンはサーバー以上にする。</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>古い pg_dump は新しいサーバーに接続できない。</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>D-11</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>手動実行</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>管理 API は作らない。BatchRunOnceRunner（--kintaiflow.batch.run-once=BAT-003）または、OS から pg_dump を直接実行（8.6）。テストでは PgDumpRunner を差し替えて BackupService#execute(LocalDate) を呼ぶ。</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>BAT-001 D-10 と同じ。</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61" ht="49" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63" ht="49" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>D-12</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>複数インスタンス</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>現状は単一インスタンス前提。将来は ShedLock（@SchedulerLock(name="BAT-003", lockAtMostFor="PT30M")）で 1 台のみ実行にする。</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>同時に 2 つ走ると同じ .tmp を書くため競合する。ShedLock 導入で防ぐ。</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62" ht="49" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="49" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>D-13</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>要件定義書の参照</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>KF-RD-001（PDF）は docs/01_要件定義 に未配置のため、保存年数は KF-BD-010 の記載（5年以上・毎日1回・7世代）に従った。</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>配置後に照合する。</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17912,7 +18018,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -19186,7 +19292,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
@@ -20554,7 +20660,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -21805,7 +21911,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>使用メソッドは ONL の疑似コード中の呼出しから抽出（実装時はコンストラクタ引数として宣言する）。</t>
+          <t>コンストラクタ引数は実コードのとおり。使用メソッドは各メソッドの処理（実コード）中の参照から抽出。</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
